--- a/config/经济配置.xlsx
+++ b/config/经济配置.xlsx
@@ -107,6 +107,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Config_economy_0" displayName="Config_economy_0" ref="A4:C9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:C9"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="商店等级"/>
     <x:tableColumn id="2" name="普通商品开放数"/>
@@ -118,6 +119,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Config_economy_1" displayName="Config_economy_1" ref="A4:D23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:D23"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="字段"/>
     <x:tableColumn id="2" name="中文含义"/>
